--- a/docs/exports/SQ1_2026_Sep_22nd_Yesly_Journey_Description.xlsx
+++ b/docs/exports/SQ1_2026_Sep_22nd_Yesly_Journey_Description.xlsx
@@ -122,7 +122,7 @@
       </c>
       <c r="I3" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -352,7 +352,7 @@
   <cols>
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="11" max="11" width="60" customWidth="1"/>
-    <col min="16" max="16" width="44" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,19 +535,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr" s="1">
+      <c r="L13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr" s="1">
+      <c r="M13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
           <t xml:space="preserve">Correction: A01 is the first-open card; the mobile number is A02. The behaviour as written is right for A02: +91 only at launch, 10 digits, 5 OTPs per hour, an inline error keeps the number editable.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="L14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">A01, A02</t>
         </is>
@@ -687,12 +687,12 @@
           <t xml:space="preserve">The OTP screen is A03. Six digits; 3 wrong codes invalidate the OTP; resend after a cooldown. The ladder in the best-practice cell is accepted as the policy: a 30-second cooldown doubling to 5 minutes, a 15 to 30 minute lockout after repeated cycles, counters and cooldowns server-side.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="L15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">A03, I08</t>
         </is>
@@ -754,12 +754,12 @@
           <t xml:space="preserve">The state router (N01). New: A04 (its placement, right after the OTP or after the first reveal questions, is to be decided on the board, W27). Returning: the state's landing screen. "Any pending mandatory step first, otherwise home" is exactly what N01 does.</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="L16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">N01, A04, W27</t>
         </is>
@@ -818,19 +818,19 @@
           <t xml:space="preserve">Yesly Comment</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr" s="1">
+      <c r="L18" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr" s="1">
+      <c r="M18" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N18" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
           <t xml:space="preserve">Accepted as proposed. A02 inline error; log the Gupshup reference.</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="L19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">A02</t>
         </is>
@@ -943,12 +943,12 @@
           <t xml:space="preserve">Accepted as proposed. A03 tells wrong from expired.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="L20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">A03</t>
         </is>
@@ -1004,12 +1004,12 @@
           <t xml:space="preserve">Accepted as proposed. Never guess the state; retry, then a "we are checking" line; the verified session stays.</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="L21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">N01</t>
         </is>
@@ -1065,7 +1065,7 @@
           <t xml:space="preserve">Accepted as proposed (FE-33, FE-37).</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr" s="2">
+      <c r="L22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -1122,12 +1122,12 @@
           <t xml:space="preserve">Accepted as proposed. +91 only at launch.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="L23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">A02</t>
         </is>
@@ -1184,12 +1184,12 @@
           <t xml:space="preserve">Accepted as proposed. The alternate channel is WhatsApp OTP (I08), in scope.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="L24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">I08</t>
         </is>
@@ -1246,12 +1246,12 @@
           <t xml:space="preserve">Accepted as proposed; show the remaining attempts.</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
+      <c r="L25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">A03</t>
         </is>
@@ -1308,12 +1308,12 @@
           <t xml:space="preserve">Accepted as proposed.</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="L26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">A03</t>
         </is>
@@ -1370,12 +1370,12 @@
           <t xml:space="preserve">Accepted as proposed; the routing is N01.</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
+      <c r="L27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">N01</t>
         </is>
@@ -1432,12 +1432,12 @@
           <t xml:space="preserve">Accepted as proposed. The minimum record is the mobile number and the verified flag. A person is a lead with a wrong OTP and a verified lead with the right one (minutes 16 Sep 2026, item 1; W26).</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
+      <c r="L28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">W26</t>
         </is>
@@ -1494,7 +1494,7 @@
           <t xml:space="preserve">Accepted as proposed, and see BE-01: one active session.</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr" s="2">
+      <c r="L29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -1551,12 +1551,12 @@
           <t xml:space="preserve">to be decided: owner Compliance (W29). Until then: not contacted, retained only as the OTP transaction log.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr" s="2">
+      <c r="L30" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">open - to be decided: owner Compliance (W29)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">W29, A02</t>
         </is>
@@ -1614,12 +1614,12 @@
           <t xml:space="preserve">No merge now: A02 and A03 are frozen. Propose it as a comment on A03 and it goes to v0.3 with the visual design. Not a build change.</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
+      <c r="L34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">A02, A03</t>
         </is>
@@ -1670,7 +1670,7 @@
   <cols>
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="11" max="11" width="60" customWidth="1"/>
-    <col min="16" max="16" width="44" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1853,19 +1853,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr" s="1">
+      <c r="L13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr" s="1">
+      <c r="M13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
           <t xml:space="preserve">Correction: the reveal is R01 to R09 (then R10 the video and R12 the sample plan; X01 is reveal saved, not paid). A04 is the welcome video (placement open, W27). A05 is the post-paywall source chooser and is not part of the reveal. Autosave per screen and resume at the first unanswered screen (S1) are on the board.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="L14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">R01, R09, X01, A04, A05, S1</t>
         </is>
@@ -1992,12 +1992,12 @@
           <t xml:space="preserve">Correction: the abandoned reveal is state S1 (signed up, no reveal); S2 is reveal seen, not paid; S4 is "data partial", after payment. The resume rule is N01 (a landing screen per state). The CRM only sends the nudge; the app decides the screen.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="L15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">S1, S2, S4, N01</t>
         </is>
@@ -2059,12 +2059,12 @@
           <t xml:space="preserve">Correction: the outcome is R09 (the reveal chart, two paths); R10 is the video; R12 the sample plan preview; then P01. Calculation unavailable: R08 shows retry and never a made-up result (accepted; it matches the board's no-assumptions rule).</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="L16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">R08, R09, R10, R12</t>
         </is>
@@ -2123,19 +2123,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr" s="1">
+      <c r="L18" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr" s="1">
+      <c r="M18" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N18" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
           <t xml:space="preserve">Accepted as proposed (state version).</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr" s="2">
+      <c r="L19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -2245,12 +2245,12 @@
           <t xml:space="preserve">Accepted as proposed; N01 wins.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="L20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">N01</t>
         </is>
@@ -2305,12 +2305,12 @@
           <t xml:space="preserve">Accepted as proposed (R08 retry).</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="L21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">R08</t>
         </is>
@@ -2366,7 +2366,7 @@
           <t xml:space="preserve">Accepted as proposed.</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr" s="2">
+      <c r="L22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -2422,12 +2422,12 @@
           <t xml:space="preserve">Accepted as proposed. Resume versus restart: always resume. After 90 days away (config) the reveal is shown again from R01 with the values prefilled for confirm-or-correct, then R08 and R09 re-run.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="L23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">R01, S1</t>
         </is>
@@ -2482,12 +2482,12 @@
           <t xml:space="preserve">Accepted as proposed; R08 and R09 re-run.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="L24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">R08</t>
         </is>
@@ -2543,7 +2543,7 @@
           <t xml:space="preserve">Accepted as proposed (Continue disabled).</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr" s="2">
+      <c r="L25" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -2599,12 +2599,12 @@
           <t xml:space="preserve">The reveal has no cross-field rule beyond the ranges (income, saved and savings rate are bands). No clarification question; the ranges are the validation.</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="L26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">R03, R04, R05</t>
         </is>
@@ -2660,12 +2660,12 @@
           <t xml:space="preserve">Accepted as proposed (the router).</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
+      <c r="L27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">N01</t>
         </is>
@@ -2721,7 +2721,7 @@
           <t xml:space="preserve">The 90-day rule in E5.</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr" s="2">
+      <c r="L28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -2777,7 +2777,7 @@
           <t xml:space="preserve">Accepted as proposed.</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr" s="2">
+      <c r="L29" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -2847,12 +2847,12 @@
           <t xml:space="preserve">Does not apply: A04 and A05 are not two intro states (see W1). R01 to R12 froze as drawn on 17 Sep 2026; no merges now.</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
+      <c r="L34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">A04, A05</t>
         </is>
@@ -2903,7 +2903,7 @@
   <cols>
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="11" max="11" width="60" customWidth="1"/>
-    <col min="16" max="16" width="44" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3086,19 +3086,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr" s="1">
+      <c r="L13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr" s="1">
+      <c r="M13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
           <t xml:space="preserve">Accepted as proposed. The SKU cards are config (I15): DIY and DIWM, monthly or quarterly, prices "Rs ___" until set; no DIFM card. Revalidate price and availability at checkout, as proposed.</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="L14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">P01, I15</t>
         </is>
@@ -3233,12 +3233,12 @@
           <t xml:space="preserve">Correction of order: P04 is the payment; P03 is the agreement and eSign and comes before the payment; P05 is "you're in". Razorpay rules: FE-40, FE-41, FE-X3.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="L15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">P03, P04, P05</t>
         </is>
@@ -3304,12 +3304,12 @@
           <t xml:space="preserve">P03. The eSign vendor is I07 (open, W34). The agreement version is stored with the eSign reference; the signed artefact is an audit record (I19). Accepted otherwise.</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="L16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">P03, I07, I19, W34</t>
         </is>
@@ -3375,12 +3375,12 @@
           <t xml:space="preserve">Correction: P02 is on every paid path (name as per PAN, PAN, date of birth, email). It is a KRA fetch to prefill the agreement, not a KYC gate; the address only when the record is not found; full KYC for execution is E02. The order is P01, P02, P03, P04, P05.</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="L17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">P02, E02, I06</t>
         </is>
@@ -3439,19 +3439,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr" s="1">
+      <c r="L19" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr" s="1">
+      <c r="M19" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N19" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
           <t xml:space="preserve">Accepted as proposed. Note: the Best Practice column of this block is shifted (it reads like the Reveal column pasted down); every answer here is against the edge case, not the cell.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr" s="2">
+      <c r="L20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -3561,12 +3561,12 @@
           <t xml:space="preserve">Accepted; re-query by order ID (FE-41).</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
+      <c r="L21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">P04</t>
         </is>
@@ -3622,12 +3622,12 @@
           <t xml:space="preserve">S2b, P03 retry; check the existing status first (FE-43).</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
+      <c r="L22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">S2b, P03</t>
         </is>
@@ -3683,12 +3683,12 @@
           <t xml:space="preserve">FE-43.</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="L23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">P02</t>
         </is>
@@ -3744,7 +3744,7 @@
           <t xml:space="preserve">FE-09.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr" s="2">
+      <c r="L24" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -3795,12 +3795,12 @@
           <t xml:space="preserve">S2 lands on X01; the offer stays; no entitlement.</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
+      <c r="L25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">S2, X01</t>
         </is>
@@ -3851,12 +3851,12 @@
           <t xml:space="preserve">The address fields on P02.</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="L26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">P02</t>
         </is>
@@ -3907,12 +3907,12 @@
           <t xml:space="preserve">Inline error, correct and retry; support through H07 (Zoho Desk) if it persists.</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
+      <c r="L27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">P02, H07</t>
         </is>
@@ -3963,12 +3963,12 @@
           <t xml:space="preserve">S2b.</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
+      <c r="L28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">S2b</t>
         </is>
@@ -4019,12 +4019,12 @@
           <t xml:space="preserve">Reconcile before any new request; a "we are checking your signing status" line on P03.</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
+      <c r="L29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">P03</t>
         </is>
@@ -4075,12 +4075,12 @@
           <t xml:space="preserve">P04 retry with another method; nothing is lost.</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
+      <c r="L30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">P04</t>
         </is>
@@ -4122,12 +4122,12 @@
           <t xml:space="preserve">Re-query first; P04 "we are confirming your payment"; never ask the person to pay again before the query.</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
+      <c r="L31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">P04</t>
         </is>
@@ -4169,12 +4169,12 @@
           <t xml:space="preserve">One idempotency key per order; P04 "already being processed".</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
+      <c r="L32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">P04</t>
         </is>
@@ -4216,12 +4216,12 @@
           <t xml:space="preserve">Q03a, state S24; the rule is BE-14 (to be decided, Compliance, W05).</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr" s="2">
+      <c r="L33" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">open - to be decided</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Q03a, S24, W05</t>
         </is>
@@ -4263,12 +4263,12 @@
           <t xml:space="preserve">Accepted as proposed. The in-app confirmation on P05 stands; the SES bounce is recorded; a CRM task asks for a corrected email (H09).</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
+      <c r="L34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">P05, I10, H09</t>
         </is>
@@ -4345,12 +4345,12 @@
           <t xml:space="preserve">No merges. P01 to P05 are frozen except P04 (open for the mandate items). P02, P03 and P04 each need an independent authoritative status, as the sheet itself says.</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
+      <c r="L40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">P01, P02, P03, P04, P05</t>
         </is>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="R12" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="R17" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
   <cols>
     <col min="9" max="9" width="60" customWidth="1"/>
     <col min="11" max="11" width="60" customWidth="1"/>
-    <col min="16" max="16" width="44" customWidth="1"/>
+    <col min="12" max="12" width="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5495,19 +5495,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr" s="1">
+      <c r="L13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr" s="1">
+      <c r="M13" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N13" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -5571,12 +5571,12 @@
           <t xml:space="preserve">Accepted as proposed, plus: the four ways are AA, CAS, type it in, not now; AA is the default card; A05a is the bank-slow state; every way lands on D01 (rule 1).</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
+      <c r="L14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">A05, A05a, D01</t>
         </is>
@@ -5642,12 +5642,12 @@
           <t xml:space="preserve">Correction: A06 is the consent (Finvu's flow); A07 is the fetching progress screen, opened from the pill. The return from A06 lands on D01 and the fetch runs in the background (Vatsal, 11 Sep 2026). Consent scope, purpose and expiry are shown in plain words above the webview (12 months, quarterly, read-only; to be verified: the maximum validity). Excluded accounts are recorded.</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
+      <c r="L15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">A06, A07, D01</t>
         </is>
@@ -5713,12 +5713,12 @@
           <t xml:space="preserve">Correction: the fetch is server-side (A07 shows the progress). A08 is the review sheet "here is what came through": include and exclude per account, an override with a source lock, the as-of date and the source per record. Holdings are stored at ISIN level with units, value and SIP mandates (needed for I02).</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
+      <c r="L16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">A07, A08, I02</t>
         </is>
@@ -5785,12 +5785,12 @@
           <t xml:space="preserve">Correction: A09 is the partial-or-failed screen: rows per FIP with retry, the CAS and manual ways, "continue with what we have" lands on D01. The imported-versus-manual precedence is A08's lock rule (BE-03).</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
+      <c r="L17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">A09, A08, D01</t>
         </is>
@@ -5857,12 +5857,12 @@
           <t xml:space="preserve">Accepted as proposed. A10 is the how-to (where to request the file). The CAS source closes with W11 (registrar CAS first, depository CAS next).</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
+      <c r="L18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">A10, W11, I23</t>
         </is>
@@ -5929,12 +5929,12 @@
           <t xml:space="preserve">Correction: A10a is the wait for the email (state S17; it waits and reminds, nothing reads an inbox); A10b is the upload with the password. Parsing is server-side (I23, open). Parse failure, PAN mismatch and several investors are accepted as separate outcomes.</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
+      <c r="L19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">A10a, A10b, S17, I23</t>
         </is>
@@ -6001,12 +6001,12 @@
           <t xml:space="preserve">Accepted as proposed. The parsed holdings are confirmed on A10c, tagged CAS-verified, with source and as-of stored; the original parse is kept apart from the confirmed values.</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
+      <c r="L20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">A10c</t>
         </is>
@@ -6065,19 +6065,19 @@
           <t xml:space="preserve">Yesly Comments</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr" s="1">
+      <c r="L22" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr" s="1">
+      <c r="M22" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N22" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -6132,12 +6132,12 @@
           <t xml:space="preserve">Accepted as proposed (A05a, A09).</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="L23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">A05a, A09</t>
         </is>
@@ -6194,12 +6194,12 @@
           <t xml:space="preserve">Accepted as proposed; abandoned lands on D01 as a manual user with aa_status not_connected; the re-asks are at G12a and Q01.</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
+      <c r="L24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">A06, D01, G12a, Q01</t>
         </is>
@@ -6256,12 +6256,12 @@
           <t xml:space="preserve">Accepted as proposed. What came through is tagged AA-fed; the rest is typed on the spine, where the D02 rows show "not fetched".</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
+      <c r="L25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">A09, D02</t>
         </is>
@@ -6318,12 +6318,12 @@
           <t xml:space="preserve">Accepted as proposed; the rule exists (A08 lock, the diff on refresh, BE-03).</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
+      <c r="L26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">A08</t>
         </is>
@@ -6380,7 +6380,7 @@
           <t xml:space="preserve">Accepted as proposed.</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr" s="2">
+      <c r="L27" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">frozen</t>
         </is>
@@ -6431,19 +6431,19 @@
           <t xml:space="preserve">Failure / Fallback</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr" s="1">
+      <c r="L30" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr" s="1">
+      <c r="M30" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Board ref</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Changed since previous export (first export 26 Sep 2026)</t>
+      <c r="N30" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Changed since 26 Sep 2026</t>
         </is>
       </c>
     </row>
@@ -6483,12 +6483,12 @@
           <t xml:space="preserve">Accepted as proposed (the autosave and state service; version check as proposed).</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
+      <c r="L31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">N01</t>
         </is>
@@ -6530,12 +6530,12 @@
           <t xml:space="preserve">Accepted as proposed: the DPDP notice, the AA consent, the contact consent from A02, the agreement version.</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
+      <c r="L32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">A02, A06, P03</t>
         </is>
@@ -6577,12 +6577,12 @@
           <t xml:space="preserve">Accepted as proposed (Finvu, I01; server-side).</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
+      <c r="L33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">I01</t>
         </is>
@@ -6624,12 +6624,12 @@
           <t xml:space="preserve">The financial profile lands in HoA Core Platform through its data-in APIs (I04, W03), with bands or midpoints as the input shape and source and precision per field. Spinach aligns API-09 with that contract rather than defining a second one.</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
+      <c r="L34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">I04, W03</t>
         </is>
@@ -6706,12 +6706,12 @@
           <t xml:space="preserve">A06 and A07 are not sequential screens (A07 opens from the pill); A08 is a sheet over the spine and A09 the failure screen. No merges.</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">frozen</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
+      <c r="L40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">frozen</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">A06, A07, A08, A09</t>
         </is>

--- a/docs/exports/SQ1_2026_Sep_22nd_Yesly_Journey_Description.xlsx
+++ b/docs/exports/SQ1_2026_Sep_22nd_Yesly_Journey_Description.xlsx
@@ -1548,7 +1548,8 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">to be decided: owner Compliance (W29). Until then: not contacted, retained only as the OTP transaction log.</t>
+          <t xml:space="preserve">to be decided: owner Compliance (W29). Until then: not contacted, retained only as the OTP transaction log.
+Update, Vatsal, 28 Sep 2026: With compliance - will revert in 2 weeks. Ideally on the LOGIN page itself there is a tick box for consent (pre-ticked) which the user may untick to release consent at this stage.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -1559,6 +1560,11 @@
       <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">W29, A02</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1617,8 @@
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">No merge now: A02 and A03 are frozen. Propose it as a comment on A03 and it goes to v0.3 with the visual design. Not a build change.</t>
+          <t xml:space="preserve">No merge now: A02 and A03 are frozen. Propose it as a comment on A03 and it goes to v0.3 with the visual design. Not a build change.
+Update, Vatsal, 28 Sep 2026: agreed</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
@@ -1622,6 +1629,11 @@
       <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">A02, A03</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4225,8 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Q03a, state S24; the rule is BE-14 (to be decided, Compliance, W05).</t>
+          <t xml:space="preserve">Q03a, state S24; the rule is BE-14 (to be decided, Compliance, W05).
+Update, Vatsal, 28 Sep 2026: with compliance - will revert in 2 weeks</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -4224,6 +4237,11 @@
       <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Q03a, S24, W05</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
     </row>
